--- a/public/post/drafts/weekly-picks/2025Lillehammer/men-points_normalized.xlsx
+++ b/public/post/drafts/weekly-picks/2025Lillehammer/men-points_normalized.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
-    <t xml:space="preserve">90.7366819821946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.9726673568761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4841831970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">242.193532536129</t>
+    <t xml:space="preserve">85.810931718363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.972667357215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5714762692951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.355075344873</t>
   </si>
   <si>
     <t xml:space="preserve">Johannes Høsflot Klæbo</t>
@@ -68,76 +68,136 @@
     <t xml:space="preserve">100</t>
   </si>
   <si>
-    <t xml:space="preserve">200</t>
+    <t xml:space="preserve">96.3138933025724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.313893302572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simen Hegstad Krüger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2577495454879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2284106989238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.486160244412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federico Pellegrino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0328716405622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3027606087962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1635264144838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.499158663842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gus Schumacher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4966076717217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4160415206469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1605800633242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.073229255693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Vermeulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.1540645037985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4345972803637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.7096677698315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.298329553994</t>
   </si>
   <si>
     <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
   </si>
   <si>
-    <t xml:space="preserve">97.799507004695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9756382399568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.775145244652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simen Hegstad Krüger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7308212212451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.730821221245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federico Pellegrino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7214732286681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3027606085718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8797485168645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.903982354104</t>
+    <t xml:space="preserve">78.6182848308447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9684835307268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.586768361572</t>
   </si>
   <si>
     <t xml:space="preserve">Pål Golberg</t>
   </si>
   <si>
-    <t xml:space="preserve">73.5988335153985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2183001579101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.817133673309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mika Vermeulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9647840396408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4345972806926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9850797457914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.384461066125</t>
+    <t xml:space="preserve">64.6606562717628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0730982461149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.733754517878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Thomas Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.4981373344468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0601920911533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.5583294256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erik Valnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6022626949922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0358378752848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.638100570277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Didrik Tønseth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6944577927847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6197305944968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.314188387281</t>
   </si>
   <si>
     <t xml:space="preserve">Friedrich Moch</t>
@@ -146,55 +206,13 @@
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
-    <t xml:space="preserve">78.9984304303768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8791854131908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.877615843568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Didrik Tønseth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7192266714205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6154574300054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.334684101426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gus Schumacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.4452943862566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4160415207089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0600135081371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.921349415103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erik Valnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6022626949436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8209371047735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.423199799717</t>
+    <t xml:space="preserve">66.9873956995706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3908273108369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.378223010407</t>
   </si>
   <si>
     <t xml:space="preserve">William Poromaa</t>
@@ -203,40 +221,40 @@
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7319560917254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.403665194976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.135621286701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Thomas Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9593707010809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8485963433246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.807967044405</t>
+    <t xml:space="preserve">50.6676473697432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2796072046304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.947254574374</t>
   </si>
   <si>
     <t xml:space="preserve">Ben Ogden</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917668548458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.1160721205777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.591673350851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.699512326275</t>
+    <t xml:space="preserve">13.4760277485717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.1160721208336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.581699330846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.173799200251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andreas Fjorden Ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1791516147019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9728933775831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.152044992285</t>
   </si>
   <si>
     <t xml:space="preserve">Andrew Musgrave</t>
@@ -245,28 +263,64 @@
     <t xml:space="preserve">Great Britain</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8770365772475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56025503057849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1839199339389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.621211541765</t>
+    <t xml:space="preserve">43.1801052893099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56025503023251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4480072552899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.188367574832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edvin Anger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9212331389096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8167808588576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.738013997767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zanden McMullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.428174721662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8784397021206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3570130118037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.663627435586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Chanavat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3243833929585</t>
   </si>
   <si>
     <t xml:space="preserve">Calle Halfvarsson</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2988415691363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.1870123874869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.485853956623</t>
+    <t xml:space="preserve">32.8355994636221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7864542878277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6220537514497</t>
   </si>
   <si>
     <t xml:space="preserve">Antoine Cyr</t>
@@ -275,85 +329,604 @@
     <t xml:space="preserve">Canada</t>
   </si>
   <si>
-    <t xml:space="preserve">36.666587569584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8537275771726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9331631499168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.453478296673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edvin Anger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9212331386985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.657451996513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5786851352115</t>
+    <t xml:space="preserve">24.8657916871789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8537275772557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5835282674214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.303047531856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Even Northug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9965637582437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iivo Niskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5198170882803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93386141649251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0056852179998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4593637227727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håvard Solås Taugbøl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.027523589742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joni Mäki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3700346053697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05946178064871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.4294963860184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florian Notz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3974420132278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6775644110455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0750064242733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauri Vuorinen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1378283053121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7208794853387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8587077906508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Häggström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2955580562001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661213160097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0616793722097</t>
   </si>
   <si>
     <t xml:space="preserve">Hugo Lapalus</t>
   </si>
   <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.8990864936746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1776486048236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0767350984982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Chanavat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3243833930608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Even Northug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9965637581809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iivo Niskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9364516804149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9338614164654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2666208123949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1369339092752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joni Mäki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3700346050875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7956341339509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1656687390383</t>
+    <t xml:space="preserve">52.6189338895311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3256932554832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9446271450143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davide Graz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4130629842498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3577744837713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7654355595426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5362730275637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaud Jay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2535705336811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Lapierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.675795567847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57652569796989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2523212658169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truls Gisselman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9921892938089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6854140900658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6776033838748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Davies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6267003545982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6857249713282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3124253259264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iver Tildheim Andersen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0014107425476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irineu Esteve Altimiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andorra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5432108200729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2207139388575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7639247589304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Clinton Schoonmaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9860717062536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naoto Baba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2332132964005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9885440738717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2217573702722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elia Barp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.488679779312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0752990321794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3196021642991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8835809757905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathis Desloges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2251976460564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63403942960246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8592370756589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattis Stenshagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9897044003447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2477991663039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2375035666487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Chappaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0196901165564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.220458460269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76945697029476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0096055471202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arsi Ruuskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3203642815421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43794192018961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7583062017317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Hellweger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1440943708213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Danielsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6561706580677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anian Sossau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4118469404729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0698944144936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34498450107104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8267258560375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleksander Holmboe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6434453048608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesco De Fabiani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9439918322257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4138115066437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3578033388694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo Schely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0457204945513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2016718691859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2473923637372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8310395844446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3504290489067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1814686333513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matz William Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5884698428329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Johannes Alev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3497782613548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7662411124981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1160193738529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oskar Svensson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6483183455481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ansgar Evensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7337956672455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Simenc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2079142642566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86907297249715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4082502459011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4852374826548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Lindholm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3949399909012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85359074191224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2485307328134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Grate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4626677565754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håvard Moseby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2981872472419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hollmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9247697566848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.107927407898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0326971645828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janosch Brugger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97550015803432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95488053045484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4671843061899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.397564994679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1277641197048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8408174642114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46153653685133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4301181207676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sivert Wiig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0797379192388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Jouve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8604749767171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Stoelben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1720703121227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier Leveille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9768709758244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77591778634489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7527887621692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niilo Moilanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5841737718269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63603480959828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2202085814252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zak Ketterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54457096432773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11544010246319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20540882527929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8654198920702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondrej Cerny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2973954045205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Bourdin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08523166843099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7780954001008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8633270685318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludek Seller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5532029610601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simone Dapra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3981792405865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37202980573054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41929526440462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1895043107217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Måns Skoglund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3666469183003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauri Lepistö</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.208154956371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406437535605468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55419452096546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1687870129419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Myhlback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3696126145022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49534773925661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8649603537588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryo Hirose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2784344010314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77739145203634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558258530677</t>
   </si>
   <si>
     <t xml:space="preserve">Beda Klee</t>
@@ -362,598 +935,130 @@
     <t xml:space="preserve">Switzerland</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8843558733286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8214771282528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7058330015814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Håvard Solås Taugbøl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0275235895301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Häggström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2955580558366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9516721862083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.247230242045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Lapierre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9663242043915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20487575854799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1711999629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Vuorinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1378283049145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4233956759145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5612239808289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iver Tildheim Andersen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3726531857047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davide Graz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0415566976671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3577744838411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8991145843215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2984457658297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renaud Jay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2535705333789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965959526999006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2195300603779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesco De Fabiani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9439918325281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4033368634466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3473286959747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florian Notz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6892639791362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6284879408639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3177519200001</t>
+    <t xml:space="preserve">1.64742601976219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8126504375473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4600764573094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Ekberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0327401802724</t>
   </si>
   <si>
     <t xml:space="preserve">Cyril Fähndrich</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5651432037052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91740996097899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1684144405435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6509676052277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naoto Baba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3080783667739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9374251093538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2455034761277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zanden McMullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7013505009059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8784397023037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1306237986314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.710414001841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elia Barp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3181917603802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0752990322416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2033924342383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.59688322686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattis Stenshagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2543911268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2477991663638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5021902932437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Clinton Schoonmaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9860717059106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Hellweger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1440943707427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18229748727229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.326391858015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irineu Esteve Altimiras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andorra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6787625442881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0228947079915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7016572522796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Chappaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8262313371133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204584601319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4376255120598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.484315309305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Jouve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8604749764171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4560405707297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3165155471468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theo Schely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0457204945501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6729851705504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7187056651005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Danielsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.656170658034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aleksander Holmboe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6434453053862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matz William Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.588469842729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oskar Svensson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6483183452819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Håvard Moseby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8841543072078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ansgar Evensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7337956669737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anian Sossau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92717653264106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0698944145239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64971723565692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6467881828218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8104967216057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3476093062785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1581060278842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Grate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4626677563618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0780192985934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.840817464317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08168804354484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0005248064552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Stoelben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12952808647415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1720703121491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45938233467844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7609807333017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Lindholm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2832547562227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.420269403674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7035241598967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truls Gisselman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6403143110787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8686432100548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5089575211336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simone Dapra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2744814951664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37202980583014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01415021145732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6606615124539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sivert Wiig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0797379193506</t>
+    <t xml:space="preserve">8.91740996076324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64058547363534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5579954343986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Wonders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72605210846997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83955757548333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5656096839533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albert Kuchler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1482272767541</t>
   </si>
   <si>
     <t xml:space="preserve">Paolo Ventura</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5093820427775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11235000714831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6217320499258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arsi Ruuskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5142053989606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75983924256411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2740446415247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niilo Moilanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5841737716777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92721166648413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5113854381619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albert Kuchler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3154224141202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6993955470577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0148179611779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Bourdin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08523166847608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.014278089399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.099509757875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ondrej Cerny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.297395404417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Davies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6800538003732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1069913312224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7870451315956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludek Seller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5532029609981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zak Ketterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19178712104919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11544010249641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71259419263434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0198214161799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvar Myhlback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30987814157995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3088420584882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6187202000682</t>
+    <t xml:space="preserve">8.18079104391584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928211362327646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10900240624349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marko Kilp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96245266238689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnus Øyaas Håbrekke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43859016753701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier McKeever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417102941937175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35563316024405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31252100801616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08525711019738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Liekari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6841121789931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matyas Bauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89320422551477</t>
   </si>
   <si>
     <t xml:space="preserve">Johnny Hagenbuch</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1007950558301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61063713985585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72112224996917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4325544456551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter Wonders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4724496235829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56564722018528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0380968437682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryo Hirose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57286631021498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13340224334811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7062685535631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janosch Brugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2878453288193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95488053061869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74940822801229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9921340874503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Lepistö</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4645545387711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406437535657065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0840779508896528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550700253178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hollmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5780543877297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90391881681683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4819732045465</t>
+    <t xml:space="preserve">5.6106371396872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Himma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6456003228911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simeon Deyanov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35177311608452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominik Bury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96685704150533</t>
   </si>
   <si>
     <t xml:space="preserve">Vitaliy Pukhkalo</t>
@@ -962,304 +1067,154 @@
     <t xml:space="preserve">Kazakhstan</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78733217709479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55772734225986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3450595193546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Liekari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68411217905463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60849834925874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2926105283134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivier Leveille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47464068904277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85443603218886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32907672123163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathis Desloges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79364897987803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31307084907993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10671982895796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marko Kilp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96245266245571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Simenc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86907297261518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvar Johannes Alev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91666743422098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824877060892515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7415444951135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnus Øyaas Håbrekke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43859016784468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andreas Fjorden Ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94336599349005</t>
+    <t xml:space="preserve">3.09215875913276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haruki Yamashita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70838046576422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636753393217962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34513385898218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri Tuz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2677988275976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79582733639708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eero Rantala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712276881366283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel Gledhill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180580066145256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daito YAMAZAKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sander HAUKVIK-JENSEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einar HEDEGART</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ole Tafjord SUHRKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fredrik FODSTAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian ENDRESTAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einar Hedegart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ole Tafjord Suhrke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sander Haukvik Jensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Earnhart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180479164220706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oskar Opstad Vike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nail Bashmakov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lars Young Vik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seve De Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ji-Yeong Byun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oleksandr Lisohor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niks Saulitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jong-Won Jeong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentley Walker-Broose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Büki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Konya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anton Grahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomas Dufek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imanol Rojo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Fellner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauris Kaparkalejs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathias Holbæk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fedor Karpov</t>
   </si>
   <si>
     <t xml:space="preserve">Sasha Masson</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47927616628694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08606690902955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56534307531649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haruki Yamashita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63004972720447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89329876650735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52334849371182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin Himma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64560032306454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imanol Rojo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43235606410277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominik Bury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43078709327898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eero Rantala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29140897033067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier McKeever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88451327906502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35563316034918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2401464394142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Fellner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00273442792889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.209479844278774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21221427220767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matyas Bauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07762197348117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96713497574481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jiri Tuz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26779882785365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Gledhill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4899464747297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Earnhart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.180479164278003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oskar Opstad Vike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Måns Skoglund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nail Bashmakov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lars Young Vik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simeon Deyanov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seve De Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Ekberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ji-Yeong Byun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oleksandr Lisohor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niks Saulitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jong-Won Jeong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bentley Walker-Broose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Büki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Konya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daito YAMAZAKI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sander HAUKVIK-JENSEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einar HEDEGART</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ole Tafjord SUHRKE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fredrik FODSTAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebastian ENDRESTAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anton Grahn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomas Dufek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauris Kaparkalejs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathias Holbæk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fedor Karpov</t>
-  </si>
-  <si>
     <t xml:space="preserve">Olzhas Klimin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einar Hedegart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ole Tafjord Suhrke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sander Haukvik Jensen</t>
   </si>
   <si>
     <t xml:space="preserve">Nicolai Elde Holmboe</t>
@@ -1672,24 +1627,24 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -1701,140 +1656,140 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -1843,27 +1798,27 @@
         <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>0.554369703815855</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -1875,82 +1830,82 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -1959,27 +1914,27 @@
         <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1991,62 +1946,62 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H15" t="n">
         <v>0.895538608879911</v>
       </c>
       <c r="I15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="s">
         <v>79</v>
@@ -2063,42 +2018,42 @@
         <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="s">
         <v>88</v>
@@ -2121,199 +2076,199 @@
         <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.895538608879911</v>
       </c>
       <c r="G19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>0.140598576859704</v>
+        <v>1</v>
       </c>
       <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.232048869591992</v>
+      </c>
+      <c r="I20" t="s">
         <v>98</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.343380738512093</v>
-      </c>
-      <c r="I20" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
         <v>100</v>
       </c>
-      <c r="B21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
         <v>101</v>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>16</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.232048869591992</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>0.343380738512093</v>
+        <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>0.343380738512093</v>
+        <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.343380738512093</v>
       </c>
       <c r="G24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0.343380738512093</v>
       </c>
       <c r="I24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="F25" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="s">
         <v>118</v>
@@ -2324,7 +2279,7 @@
         <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
         <v>16</v>
@@ -2339,79 +2294,79 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.203941216842155</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="F28" t="n">
-        <v>0.23180786429876</v>
+        <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H28" t="n">
-        <v>0.126322714192866</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -2420,30 +2375,30 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -2452,53 +2407,53 @@
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.140598576859704</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.343380738512093</v>
       </c>
       <c r="I30" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F31" t="n">
         <v>0.47308066914478</v>
       </c>
       <c r="G31" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H31" t="n">
         <v>0.779978161976048</v>
       </c>
       <c r="I31" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
         <v>16</v>
@@ -2507,59 +2462,59 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="H32" t="n">
         <v>0.382583907138237</v>
       </c>
       <c r="I32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.23180786429876</v>
       </c>
       <c r="G33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.126322714192866</v>
       </c>
       <c r="I33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -2568,53 +2523,53 @@
         <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>0.203941216842155</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H35" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
         <v>159</v>
@@ -2626,256 +2581,256 @@
         <v>16</v>
       </c>
       <c r="F36" t="n">
-        <v>0.558971169677543</v>
+        <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" t="s">
         <v>162</v>
       </c>
-      <c r="B37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
         <v>163</v>
       </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
         <v>164</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.895538608879911</v>
-      </c>
-      <c r="G37" t="s">
-        <v>165</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F38" t="n">
-        <v>0.779978161976048</v>
+        <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="H38" t="n">
-        <v>0.47308066914478</v>
+        <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>172</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>174</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.779978161976048</v>
+      </c>
+      <c r="G40" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.47308066914478</v>
+      </c>
+      <c r="I40" t="s">
         <v>176</v>
-      </c>
-      <c r="B40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
-        <v>177</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" t="s">
         <v>178</v>
       </c>
-      <c r="B41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" t="s">
-        <v>16</v>
-      </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
         <v>179</v>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="H41" t="n">
+        <v>0.208270945862351</v>
+      </c>
+      <c r="I41" t="s">
         <v>180</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" t="s">
         <v>182</v>
       </c>
-      <c r="B42" t="s">
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
         <v>183</v>
       </c>
-      <c r="C42" t="s">
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="s">
         <v>184</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>16</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>185</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>185</v>
+      </c>
+      <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
         <v>187</v>
-      </c>
-      <c r="B43" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" t="s">
-        <v>188</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>189</v>
       </c>
       <c r="F43" t="n">
         <v>0.382186556584935</v>
       </c>
       <c r="G43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H43" t="n">
         <v>0.0766185991760893</v>
       </c>
       <c r="I43" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>190</v>
+      </c>
+      <c r="B44" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0766185991760893</v>
+      </c>
+      <c r="G44" t="s">
         <v>192</v>
       </c>
-      <c r="B44" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="H44" t="n">
+        <v>0.208270945862351</v>
+      </c>
+      <c r="I44" t="s">
         <v>193</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.630774225526373</v>
-      </c>
-      <c r="G44" t="s">
-        <v>194</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.630774225526373</v>
-      </c>
-      <c r="I44" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
         <v>16</v>
@@ -2884,27 +2839,27 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F45" t="n">
-        <v>0.382583907138237</v>
+        <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
         <v>16</v>
@@ -2913,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -2925,41 +2880,41 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>198</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" t="s">
+        <v>199</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>200</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>201</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.336242222180128</v>
+      </c>
+      <c r="I47" t="s">
         <v>202</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>16</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="s">
-        <v>203</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
@@ -2971,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -2983,44 +2938,44 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
         <v>206</v>
       </c>
-      <c r="B49" t="s">
-        <v>62</v>
-      </c>
-      <c r="C49" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
         <v>207</v>
       </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>16</v>
-      </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
         <v>16</v>
@@ -3029,88 +2984,88 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="G50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>214</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>216</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
+        <v>16</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>215</v>
+        <v>16</v>
       </c>
       <c r="H52" t="n">
-        <v>0.336242222180128</v>
+        <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B53" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C53" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
@@ -3119,24 +3074,24 @@
         <v>16</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="G53" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
         <v>16</v>
@@ -3145,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -3157,33 +3112,33 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>227</v>
+        <v>16</v>
       </c>
       <c r="H55" t="n">
-        <v>0.669620389113773</v>
+        <v>0</v>
       </c>
       <c r="I55" t="s">
         <v>228</v>
@@ -3194,39 +3149,39 @@
         <v>229</v>
       </c>
       <c r="B56" t="s">
-        <v>43</v>
+        <v>230</v>
       </c>
       <c r="C56" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H56" t="n">
-        <v>0.203941216842155</v>
+        <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C57" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -3238,155 +3193,155 @@
         <v>0.126322714192866</v>
       </c>
       <c r="G57" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H57" t="n">
         <v>0.126322714192866</v>
       </c>
       <c r="I57" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>239</v>
+        <v>16</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="s">
         <v>240</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
         <v>242</v>
       </c>
-      <c r="B59" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" t="s">
-        <v>243</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>244</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.286937930353677</v>
-      </c>
-      <c r="G59" t="s">
-        <v>245</v>
-      </c>
       <c r="H59" t="n">
-        <v>0.174036652193994</v>
+        <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>248</v>
+        <v>16</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0.788467781907967</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
+        <v>245</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>247</v>
+      </c>
+      <c r="B61" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" t="s">
+        <v>248</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
         <v>249</v>
       </c>
-      <c r="B61" t="s">
-        <v>27</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="F61" t="n">
+        <v>0.914001122512931</v>
+      </c>
+      <c r="G61" t="s">
         <v>250</v>
       </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="s">
-        <v>16</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.174036652193994</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="H61" t="n">
+        <v>0.914001122512931</v>
+      </c>
+      <c r="I61" t="s">
         <v>251</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.286937930353677</v>
-      </c>
-      <c r="I61" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>252</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
         <v>253</v>
       </c>
-      <c r="B62" t="s">
-        <v>105</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
         <v>254</v>
       </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
-        <v>16</v>
-      </c>
       <c r="F62" t="n">
-        <v>0.0766185991760893</v>
+        <v>1</v>
       </c>
       <c r="G62" t="s">
         <v>255</v>
       </c>
       <c r="H62" t="n">
-        <v>0.208270945862351</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I62" t="s">
         <v>256</v>
@@ -3397,7 +3352,7 @@
         <v>257</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="C63" t="s">
         <v>16</v>
@@ -3409,288 +3364,288 @@
         <v>258</v>
       </c>
       <c r="F63" t="n">
-        <v>0.630774225526373</v>
+        <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="H63" t="n">
-        <v>0.382583907138237</v>
+        <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="C64" t="s">
-        <v>262</v>
+        <v>16</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="F64" t="n">
-        <v>0.336242222180128</v>
+        <v>0.630774225526373</v>
       </c>
       <c r="G64" t="s">
-        <v>263</v>
+        <v>16</v>
       </c>
       <c r="H64" t="n">
-        <v>0.554369703815855</v>
+        <v>0.630774225526373</v>
       </c>
       <c r="I64" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C65" t="s">
         <v>16</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F65" t="n">
-        <v>0.232048869591992</v>
+        <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>267</v>
+        <v>16</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0.203941216842155</v>
       </c>
       <c r="I65" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B66" t="s">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>264</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0.290061086989989</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>265</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0.478229883922796</v>
       </c>
       <c r="I66" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C67" t="s">
-        <v>273</v>
+        <v>16</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>0.630774225526373</v>
       </c>
       <c r="G67" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="I67" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B68" t="s">
-        <v>270</v>
+        <v>31</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0.329450242982193</v>
       </c>
       <c r="G68" t="s">
-        <v>16</v>
+        <v>274</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0.543171623242067</v>
       </c>
       <c r="I68" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>276</v>
+      </c>
+      <c r="B69" t="s">
+        <v>277</v>
+      </c>
+      <c r="C69" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
         <v>278</v>
       </c>
-      <c r="B69" t="s">
-        <v>52</v>
-      </c>
-      <c r="C69" t="s">
-        <v>279</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="s">
-        <v>280</v>
-      </c>
       <c r="F69" t="n">
-        <v>0.329450242982193</v>
+        <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>281</v>
+        <v>16</v>
       </c>
       <c r="H69" t="n">
-        <v>0.543171623242067</v>
+        <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>284</v>
+        <v>16</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>16</v>
+        <v>280</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="G70" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>277</v>
       </c>
       <c r="C71" t="s">
-        <v>288</v>
+        <v>16</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F71" t="n">
-        <v>0.543171623242067</v>
+        <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>290</v>
+        <v>16</v>
       </c>
       <c r="H71" t="n">
-        <v>0.121197971282085</v>
+        <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>16</v>
+        <v>287</v>
       </c>
       <c r="F72" t="n">
-        <v>0.121197971282085</v>
+        <v>0.286937930353677</v>
       </c>
       <c r="G72" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="H72" t="n">
-        <v>0.329450242982193</v>
+        <v>0.174036652193994</v>
       </c>
       <c r="I72" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
@@ -3699,85 +3654,85 @@
         <v>16</v>
       </c>
       <c r="F73" t="n">
-        <v>0.921587657155495</v>
+        <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="H73" t="n">
-        <v>0.921587657155495</v>
+        <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F74" t="n">
-        <v>0.914001122512931</v>
+        <v>0.208270945862351</v>
       </c>
       <c r="G74" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="H74" t="n">
-        <v>0.914001122512931</v>
+        <v>0.0766185991760893</v>
       </c>
       <c r="I74" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C75" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>307</v>
+        <v>16</v>
       </c>
       <c r="F75" t="n">
-        <v>0.208270945862351</v>
+        <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0766185991760893</v>
+        <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="C76" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -3786,27 +3741,27 @@
         <v>16</v>
       </c>
       <c r="F76" t="n">
-        <v>0.788467781907967</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="G76" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="I76" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B77" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C77" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -3815,85 +3770,85 @@
         <v>16</v>
       </c>
       <c r="F77" t="n">
-        <v>0.406145296366207</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G77" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B78" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>311</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>320</v>
+        <v>16</v>
       </c>
       <c r="F78" t="n">
-        <v>0.382583907138237</v>
+        <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>321</v>
+        <v>16</v>
       </c>
       <c r="H78" t="n">
-        <v>0.232048869591992</v>
+        <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>306</v>
       </c>
       <c r="C79" t="s">
-        <v>324</v>
+        <v>16</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>16</v>
+        <v>313</v>
       </c>
       <c r="F79" t="n">
-        <v>0.290061086989989</v>
+        <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H79" t="n">
-        <v>0.478229883922796</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I79" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="C80" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
@@ -3902,24 +3857,24 @@
         <v>16</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>0.121197971282085</v>
       </c>
       <c r="G80" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="H80" t="n">
-        <v>0.208270945862351</v>
+        <v>0.329450242982193</v>
       </c>
       <c r="I80" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="B81" t="s">
-        <v>332</v>
+        <v>63</v>
       </c>
       <c r="C81" t="s">
         <v>16</v>
@@ -3928,82 +3883,82 @@
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>333</v>
+        <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0.336242222180128</v>
       </c>
       <c r="G81" t="s">
-        <v>16</v>
+        <v>321</v>
       </c>
       <c r="H81" t="n">
-        <v>0.558971169677543</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="I81" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B82" t="s">
-        <v>335</v>
+        <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>323</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>336</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0.174036652193994</v>
       </c>
       <c r="G82" t="s">
-        <v>16</v>
+        <v>324</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0.286937930353677</v>
       </c>
       <c r="I82" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="B83" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="C83" t="s">
-        <v>338</v>
+        <v>16</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>327</v>
       </c>
       <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" t="n">
         <v>0.558971169677543</v>
       </c>
-      <c r="G83" t="s">
-        <v>339</v>
-      </c>
-      <c r="H83" t="n">
-        <v>1</v>
-      </c>
       <c r="I83" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
@@ -4015,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -4027,76 +3982,76 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B85" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>331</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>332</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>0.478229883922796</v>
       </c>
       <c r="G85" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0.788467781907967</v>
       </c>
       <c r="I85" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C86" t="s">
-        <v>346</v>
+        <v>16</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>16</v>
+        <v>336</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="G86" t="s">
-        <v>347</v>
+        <v>16</v>
       </c>
       <c r="H86" t="n">
-        <v>0.290061086989989</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="I86" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B87" t="s">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="C87" t="s">
-        <v>350</v>
+        <v>16</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
@@ -4105,24 +4060,24 @@
         <v>16</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="H87" t="n">
-        <v>0.558971169677543</v>
+        <v>0.910108467846823</v>
       </c>
       <c r="I87" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="B88" t="s">
-        <v>332</v>
+        <v>31</v>
       </c>
       <c r="C88" t="s">
         <v>16</v>
@@ -4131,59 +4086,59 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="F88" t="n">
-        <v>0.921587657155495</v>
+        <v>0.543171623242067</v>
       </c>
       <c r="G88" t="s">
         <v>16</v>
       </c>
       <c r="H88" t="n">
-        <v>0.921587657155495</v>
+        <v>0.121197971282085</v>
       </c>
       <c r="I88" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="B89" t="s">
-        <v>356</v>
+        <v>221</v>
       </c>
       <c r="C89" t="s">
-        <v>357</v>
+        <v>16</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>342</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="G89" t="s">
         <v>16</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="I89" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="B90" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C90" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -4201,76 +4156,76 @@
         <v>1</v>
       </c>
       <c r="I90" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="B91" t="s">
-        <v>105</v>
+        <v>347</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>348</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="s">
         <v>16</v>
       </c>
       <c r="F91" t="n">
-        <v>0.232048869591992</v>
+        <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>362</v>
+        <v>16</v>
       </c>
       <c r="H91" t="n">
-        <v>0.630774225526373</v>
+        <v>1</v>
       </c>
       <c r="I91" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B92" t="s">
-        <v>86</v>
+        <v>350</v>
       </c>
       <c r="C92" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>365</v>
+        <v>16</v>
       </c>
       <c r="F92" t="n">
-        <v>0.478229883922796</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="G92" t="s">
         <v>16</v>
       </c>
       <c r="H92" t="n">
-        <v>0.788467781907967</v>
+        <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="B93" t="s">
-        <v>270</v>
+        <v>168</v>
       </c>
       <c r="C93" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
@@ -4279,24 +4234,24 @@
         <v>16</v>
       </c>
       <c r="F93" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="H93" t="n">
-        <v>0.552008689413187</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="I93" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B94" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C94" t="s">
         <v>16</v>
@@ -4305,30 +4260,30 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>357</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>372</v>
+        <v>16</v>
       </c>
       <c r="H94" t="n">
-        <v>0.910108467846823</v>
+        <v>0.334810194556887</v>
       </c>
       <c r="I94" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="B95" t="s">
-        <v>335</v>
+        <v>230</v>
       </c>
       <c r="C95" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -4346,47 +4301,47 @@
         <v>0.755081337596291</v>
       </c>
       <c r="I95" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B96" t="s">
-        <v>270</v>
+        <v>112</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>376</v>
+        <v>16</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="G96" t="s">
-        <v>16</v>
+        <v>361</v>
       </c>
       <c r="H96" t="n">
-        <v>0.334810194556887</v>
+        <v>0.630774225526373</v>
       </c>
       <c r="I96" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B97" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -4398,62 +4353,58 @@
         <v>0.74529489290339</v>
       </c>
       <c r="G97" t="s">
-        <v>378</v>
+        <v>16</v>
       </c>
       <c r="H97" t="n">
         <v>0.406145296366207</v>
       </c>
       <c r="I97" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>379</v>
-      </c>
-      <c r="B98" t="s">
-        <v>52</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="B98"/>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="F98" t="n">
-        <v>0.199821673218477</v>
+        <v>0</v>
       </c>
       <c r="G98" t="s">
         <v>16</v>
       </c>
       <c r="H98" t="n">
-        <v>0.199821673218477</v>
+        <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>381</v>
-      </c>
-      <c r="B99" t="s">
-        <v>10</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="B99"/>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="s">
         <v>16</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="s">
         <v>16</v>
@@ -4462,18 +4413,16 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>382</v>
-      </c>
-      <c r="B100" t="s">
-        <v>62</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B100"/>
       <c r="C100" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D100" t="n">
         <v>1</v>
@@ -4491,18 +4440,16 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>383</v>
-      </c>
-      <c r="B101" t="s">
-        <v>315</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="B101"/>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -4511,27 +4458,25 @@
         <v>16</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="s">
         <v>16</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>384</v>
-      </c>
-      <c r="B102" t="s">
-        <v>385</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="B102"/>
       <c r="C102" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -4540,27 +4485,25 @@
         <v>16</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="s">
         <v>16</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>386</v>
-      </c>
-      <c r="B103" t="s">
-        <v>387</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="B103"/>
       <c r="C103" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
@@ -4569,27 +4512,27 @@
         <v>16</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="s">
         <v>16</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="B104" t="s">
-        <v>385</v>
+        <v>10</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -4598,27 +4541,27 @@
         <v>16</v>
       </c>
       <c r="F104" t="n">
-        <v>0.558971169677543</v>
+        <v>0</v>
       </c>
       <c r="G104" t="s">
         <v>16</v>
       </c>
       <c r="H104" t="n">
-        <v>0.921587657155495</v>
+        <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="B105" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -4636,18 +4579,18 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="B106" t="s">
-        <v>391</v>
+        <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
@@ -4662,18 +4605,18 @@
         <v>16</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="B107" t="s">
-        <v>393</v>
+        <v>31</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -4682,45 +4625,45 @@
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>16</v>
+        <v>374</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0.199821673218477</v>
       </c>
       <c r="G107" t="s">
         <v>16</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0.199821673218477</v>
       </c>
       <c r="I107" t="s">
-        <v>16</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="B108" t="s">
-        <v>395</v>
+        <v>10</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
       </c>
       <c r="F108" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G108" t="s">
         <v>16</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" t="s">
         <v>16</v>
@@ -4728,10 +4671,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="B109" t="s">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -4749,7 +4692,7 @@
         <v>16</v>
       </c>
       <c r="H109" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I109" t="s">
         <v>16</v>
@@ -4757,10 +4700,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="B110" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
@@ -4772,13 +4715,13 @@
         <v>16</v>
       </c>
       <c r="F110" t="n">
-        <v>0.921587657155495</v>
+        <v>1</v>
       </c>
       <c r="G110" t="s">
         <v>16</v>
       </c>
       <c r="H110" t="n">
-        <v>0.558971169677543</v>
+        <v>1</v>
       </c>
       <c r="I110" t="s">
         <v>16</v>
@@ -4786,10 +4729,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="B111" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
@@ -4801,13 +4744,13 @@
         <v>16</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="G111" t="s">
         <v>16</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="I111" t="s">
         <v>16</v>
@@ -4815,10 +4758,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B112" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
@@ -4830,13 +4773,13 @@
         <v>16</v>
       </c>
       <c r="F112" t="n">
-        <v>0.755081337596291</v>
+        <v>0</v>
       </c>
       <c r="G112" t="s">
         <v>16</v>
       </c>
       <c r="H112" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I112" t="s">
         <v>16</v>
@@ -4844,9 +4787,11 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>401</v>
-      </c>
-      <c r="B113"/>
+        <v>382</v>
+      </c>
+      <c r="B113" t="s">
+        <v>383</v>
+      </c>
       <c r="C113" t="s">
         <v>16</v>
       </c>
@@ -4857,13 +4802,13 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="s">
         <v>16</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="s">
         <v>16</v>
@@ -4871,9 +4816,11 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>402</v>
-      </c>
-      <c r="B114"/>
+        <v>384</v>
+      </c>
+      <c r="B114" t="s">
+        <v>385</v>
+      </c>
       <c r="C114" t="s">
         <v>16</v>
       </c>
@@ -4884,13 +4831,13 @@
         <v>16</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G114" t="s">
         <v>16</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="s">
         <v>16</v>
@@ -4898,9 +4845,11 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>403</v>
-      </c>
-      <c r="B115"/>
+        <v>386</v>
+      </c>
+      <c r="B115" t="s">
+        <v>381</v>
+      </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
@@ -4911,13 +4860,13 @@
         <v>16</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" t="s">
         <v>16</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I115" t="s">
         <v>16</v>
@@ -4925,9 +4874,11 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>404</v>
-      </c>
-      <c r="B116"/>
+        <v>387</v>
+      </c>
+      <c r="B116" t="s">
+        <v>378</v>
+      </c>
       <c r="C116" t="s">
         <v>16</v>
       </c>
@@ -4938,13 +4889,13 @@
         <v>16</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="G116" t="s">
         <v>16</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="I116" t="s">
         <v>16</v>
@@ -4952,9 +4903,11 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>405</v>
-      </c>
-      <c r="B117"/>
+        <v>388</v>
+      </c>
+      <c r="B117" t="s">
+        <v>389</v>
+      </c>
       <c r="C117" t="s">
         <v>16</v>
       </c>
@@ -4965,13 +4918,13 @@
         <v>16</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="s">
         <v>16</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" t="s">
         <v>16</v>
@@ -4979,9 +4932,11 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>406</v>
-      </c>
-      <c r="B118"/>
+        <v>390</v>
+      </c>
+      <c r="B118" t="s">
+        <v>389</v>
+      </c>
       <c r="C118" t="s">
         <v>16</v>
       </c>
@@ -4992,13 +4947,13 @@
         <v>16</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G118" t="s">
         <v>16</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I118" t="s">
         <v>16</v>
@@ -5006,10 +4961,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="B119" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -5035,10 +4990,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="B120" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
@@ -5064,10 +5019,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="B121" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C121" t="s">
         <v>16</v>
@@ -5085,7 +5040,7 @@
         <v>16</v>
       </c>
       <c r="H121" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I121" t="s">
         <v>16</v>
@@ -5093,28 +5048,28 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="B122" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" t="s">
         <v>16</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G122" t="s">
         <v>16</v>
       </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>0.552008689413187</v>
       </c>
       <c r="I122" t="s">
         <v>16</v>
@@ -5122,10 +5077,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="B123" t="s">
-        <v>315</v>
+        <v>385</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
@@ -5143,7 +5098,7 @@
         <v>16</v>
       </c>
       <c r="H123" t="n">
-        <v>0.406145296366207</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I123" t="s">
         <v>16</v>
@@ -5151,28 +5106,28 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="B124" t="s">
-        <v>315</v>
+        <v>10</v>
       </c>
       <c r="C124" t="s">
         <v>16</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
       </c>
       <c r="F124" t="n">
-        <v>0.669620389113773</v>
+        <v>0</v>
       </c>
       <c r="G124" t="s">
         <v>16</v>
       </c>
       <c r="H124" t="n">
-        <v>0.669620389113773</v>
+        <v>1</v>
       </c>
       <c r="I124" t="s">
         <v>16</v>
@@ -5180,10 +5135,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="C125" t="s">
         <v>16</v>
@@ -5195,13 +5150,13 @@
         <v>16</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" t="s">
         <v>16</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="I125" t="s">
         <v>16</v>
@@ -5209,10 +5164,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="C126" t="s">
         <v>16</v>
@@ -5224,13 +5179,13 @@
         <v>16</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="s">
         <v>16</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>0.290061086989989</v>
       </c>
       <c r="I126" t="s">
         <v>16</v>
@@ -5238,10 +5193,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="C127" t="s">
         <v>16</v>
@@ -5253,13 +5208,13 @@
         <v>16</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G127" t="s">
         <v>16</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I127" t="s">
         <v>16</v>
@@ -5267,7 +5222,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="B128" t="s">
         <v>10</v>
@@ -5296,7 +5251,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="B129" t="s">
         <v>10</v>
